--- a/excel/appkpi.xlsx
+++ b/excel/appkpi.xlsx
@@ -175,11 +175,13 @@
   </si>
   <si>
     <t xml:space="preserve">描述：
-统计当月产生或激活，且未解决的bug，每个扣0.4分</t>
+统计当月产生或激活，且未解决的bug
+严重bug(严重程度1级与2级)，1个扣0.6分
+一般bug(3级以上)，扣0.4分</t>
   </si>
   <si>
     <t xml:space="preserve">
-分值=25 – (当月bug数)*0.4</t>
+分值=25 – (当月严重bug数)*0.6 – (当月一般bug数)*0.4</t>
   </si>
   <si>
     <t xml:space="preserve">团队协作
@@ -887,7 +889,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>17</v>
@@ -905,7 +907,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>20</v>

--- a/excel/appkpi.xlsx
+++ b/excel/appkpi.xlsx
@@ -170,8 +170,7 @@
     <t xml:space="preserve">分值=当月完成需求分值总和（需求状态是研发完毕）</t>
   </si>
   <si>
-    <t xml:space="preserve">项目平均
-bug关闭率</t>
+    <t xml:space="preserve">bug遗留数</t>
   </si>
   <si>
     <t xml:space="preserve">描述：
@@ -181,7 +180,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-分值=25 – (当月严重bug数)*0.6 – (当月一般bug数)*0.4</t>
+分值=30 – (当月严重bug数)*0.6 – (当月一般bug数)*0.4</t>
   </si>
   <si>
     <t xml:space="preserve">团队协作

--- a/excel/appkpi.xlsx
+++ b/excel/appkpi.xlsx
@@ -70,51 +70,15 @@
 （交付或上架）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">描述
+    <t xml:space="preserve">描述
 1、该项由于关联牵扯多方配合（嵌入式、ui设计、产品），只统计软件开发阶段的进度达成率，其他环节有其他指标来判断。（以提交版本测试创建测试单为准）
 2、APP的项目分类如下：适配的设备型号、SDK或插件、APP上架
 3、APP上架涉及的需求责任方，同样纳入项目达成率
 计算标准： 
 1. 以冲刺的计划完成时间为准
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">延时1天扣2分，扣完为止
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3. 若有其它穿插项目需要调整优先级，项目可根据客观、实际情况来调整
+2. 延时1天扣3分，扣完为止
+3. 若有其它穿插项目需要调整优先级，项目可根据客观、实际情况来调整
 4. 若规划当月能完成且不影响生产及其它项目计划，可根据实际来考评</t>
-    </r>
   </si>
   <si>
     <r>
@@ -155,7 +119,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) * 2</t>
+      <t xml:space="preserve">) * 3</t>
     </r>
   </si>
   <si>
@@ -175,12 +139,13 @@
   <si>
     <t xml:space="preserve">描述：
 统计当月产生或激活，且未解决的bug
-严重bug(严重程度1级与2级)，1个扣0.6分
-一般bug(3级以上)，扣0.4分</t>
+严重bug(严重程度1级与2级)，1个扣1分
+一般bug(3级以上)，扣0.5分
+分值=30 – (当月严重bug数)*1.0 – (当月一般bug数)*0.5</t>
   </si>
   <si>
     <t xml:space="preserve">
-分值=30 – (当月严重bug数)*0.6 – (当月一般bug数)*0.4</t>
+分值=30 – (当月严重bug数)*1 – (当月一般bug数)*0.5</t>
   </si>
   <si>
     <t xml:space="preserve">团队协作
@@ -311,7 +276,7 @@
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,19 +327,6 @@
     </font>
     <font>
       <sz val="7"/>
-      <name val="微软雅黑"/>
-      <family val="0"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <name val="宋体"/>
-      <family val="0"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <family val="0"/>
       <charset val="134"/>
@@ -519,7 +471,7 @@
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -527,19 +479,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -571,11 +523,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
